--- a/Hoadon/HD2026/HDVao/6/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/6/3502550210_HDDienTuMayTinhTien.xlsx
@@ -302,6 +302,2257 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C26MVT</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>131270</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0302249586-009</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
+        </is>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="13" t="n">
+        <v>3601850.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>288148.0</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>3889998.0</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C26MVT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>131441</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0302249586-009</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
+        </is>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="13" t="n">
+        <v>5194440.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>415555.0</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>5609995.0</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C26MTT</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>077082002684</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>3611500.0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C26MMM</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>079056002409</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Cường Hưng</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>390i, Nguyễn Duy, Phường Chánh Hưng, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>3400000.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C26MMH</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>079078009688</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH MẠNH HIẾU</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>606 Tân Kỳ Tân Quý, KP7, P.Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>4600000.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>28021</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>3.4011111E7</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>2720889.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>3462489.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>3.6732E7</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>28049</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>3384000.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>270720.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>3654720.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>28169</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13" t="n">
+        <v>1.3284E7</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>1062720.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>1.434672E7</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>28343</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
+        <v>1772150.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>141772.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>1913922.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>28344</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>1013150.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>81052.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>1094202.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>28734</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>1187784.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>95023.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>77016.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>1282807.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>28964</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>094162000021</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>4979500.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>398360.0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>5377860.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>29155</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13" t="n">
+        <v>2141300.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>171304.0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>2312604.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>29233</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>3.4722222E7</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>2777778.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>2057778.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>3.75E7</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>29420</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>7686490.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>614919.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>8301409.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C26MRV</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>29840</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3500704465</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>8033795.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>642704.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>113305.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>8676499.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C26MRT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>13993</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>1855556.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>148444.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>2004000.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C26MRT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>13994</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3501013206</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>6233248.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>581752.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>6815000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C26MTK</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502242819</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>1.7763636E7</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>1776364.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>1.954E7</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2853</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>1481482.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>118519.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>1600001.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2889</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>2222222.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>177778.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>2400000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2942</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502344144</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>9436363.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>943637.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>1.038E7</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C26MDH</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>908333.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>72667.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>981000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C26MDH</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502399055</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>1205370.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>96430.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>1301800.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C26MTT</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502425499</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NPP TOÀN THẮNG PH</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>75/9/7 Phạm Hồng Thái, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>5900000.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>472000.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>6372000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>5512</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502474552</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13" t="n">
+        <v>2727274.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>272727.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>3000001.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>5962</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502474552</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI TRỌNG GIANG</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>B16 Khu Tái Định Cư 199 Lô Khu Nhà Ở Đồi 2, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>2727274.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>272727.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>3000001.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>5.3649427E7</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>5364943.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>5.901437E7</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>1.3055556E7</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>1044444.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>1.41E7</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>6829444.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>546356.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>7375800.0</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>1407407.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>112593.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>1520000.0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
